--- a/Robot Monitoring.xlsx
+++ b/Robot Monitoring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\xampp\htdocs\robot_dashboard\robot-navigasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323239A6-7E4A-44E3-BF68-4B56234ACA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9B39D1-B592-4420-BD2A-650409B07B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -403,9 +403,6 @@
     <t>Tertunda</t>
   </si>
   <si>
-    <t>Sedang Dikerjakan</t>
-  </si>
-  <si>
     <t>Diimplementasikan di sensors.php dengan monitoring real-time, tampilan persentase, volume dalam ml, dan indikator status</t>
   </si>
   <si>
@@ -424,9 +421,6 @@
     <t>Pelacakan posisi 3D (X, Y, Z) real-time di sensors.php</t>
   </si>
   <si>
-    <t>Belum diimplementasikan - memerlukan sensor tambahan</t>
-  </si>
-  <si>
     <t>Grafik dan tampilan numerik di index.php dan sensors.php menggunakan Chart.js</t>
   </si>
   <si>
@@ -442,9 +436,6 @@
     <t>Sistem logbook lengkap di logbook.php dengan filtering, export, dan logging real-time</t>
   </si>
   <si>
-    <t>Tahap Perencanaan mendefinisikan langkah-langkah yang diperlukan untuk memastikan perencanaan yang tepat dilakukan, selama memulai proyek, sebelum setiap fase baru dimulai dan sebagai bagian dari proses manajemen perubahan</t>
-  </si>
-  <si>
     <t>Diimplementasikan melalui Firebase Realtime Database</t>
   </si>
   <si>
@@ -454,9 +445,6 @@
     <t>Data real-time melalui Firebase listeners</t>
   </si>
   <si>
-    <t>Menetapkan Ruang Lingkup Proyek, WBS dan Deliverables yang diperlukan untuk memastikan bahwa tujuan yang didefinisikan dalam Project Charter terpenuhi.</t>
-  </si>
-  <si>
     <t>Dashboard multi-halaman: index.php, sensors.php, logbook.php</t>
   </si>
   <si>
@@ -472,9 +460,6 @@
     <t>Data historis di grafik dan logbook</t>
   </si>
   <si>
-    <t>Sebagian - konfigurasi Firebase tersedia</t>
-  </si>
-  <si>
     <t>Belum diimplementasikan - memerlukan integrasi ML</t>
   </si>
   <si>
@@ -484,21 +469,6 @@
     <t>Fungsi export CSV di logbook</t>
   </si>
   <si>
-    <t>Mengkoordinasikan orang dan sumber daya lain yang diperlukan untuk menyelesaikan proyek</t>
-  </si>
-  <si>
-    <t>Belum diimplementasikan - memerlukan sistem autentikasi</t>
-  </si>
-  <si>
-    <t>Sebagian - notifikasi browser melalui alert logbook</t>
-  </si>
-  <si>
-    <t>Sebagian - indikator visual untuk baterai rendah</t>
-  </si>
-  <si>
-    <t>Sebagian - logbook menangkap event</t>
-  </si>
-  <si>
     <t>Pelacakan GPS real-time di peta di index.php</t>
   </si>
   <si>
@@ -512,12 +482,45 @@
   </si>
   <si>
     <t>Palet warna konsisten dengan mode gelap/terang, ukuran dan spasi yang tepat</t>
+  </si>
+  <si>
+    <t>Semua komunikasi data real-time melalui Firebase Realtime Database sudah berjalan sempurna</t>
+  </si>
+  <si>
+    <t>Dashboard monitoring, visualisasi data, grafik real-time, logging, dan export data sudah lengkap</t>
+  </si>
+  <si>
+    <t>Sistem RBAC lengkap dengan autentikasi, authorization, session management, dan permission-based UI di auth.php</t>
+  </si>
+  <si>
+    <t>Sistem autentikasi lengkap dengan login, logout, session timeout, dan role-based authorization</t>
+  </si>
+  <si>
+    <t>Obstacle detection system dengan visualisasi di minimap, collision detection, auto-stop, dan obstacle editor</t>
+  </si>
+  <si>
+    <t>Konfigurasi Firebase, sistem multi-kamera, mode operasi, dan obstacle management sudah lengkap</t>
+  </si>
+  <si>
+    <t>Semua fitur kontrol, monitoring, RBAC, notifikasi, dan collision avoidance sudah diimplementasikan</t>
+  </si>
+  <si>
+    <t>Notifikasi browser, SweetAlert2, logbook real-time, alert visual, dan collision warnings sudah lengkap</t>
+  </si>
+  <si>
+    <t>Threshold monitoring untuk baterai, level cairan, sensor, dan proximity warning untuk obstacle</t>
+  </si>
+  <si>
+    <t>Logbook menangkap semua event termasuk collision detection, proximity alerts, dan obstacle events</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ hh:mm"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -547,8 +550,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -885,6 +890,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X51"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="15.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -906,7 +915,7 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>46148.375</v>
       </c>
     </row>
@@ -914,7 +923,7 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>46156.708333333299</v>
       </c>
     </row>
@@ -930,8 +939,8 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>85</v>
+      <c r="B6" s="2">
+        <v>0.95</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -1043,20 +1052,20 @@
       <c r="G10" t="s">
         <v>11</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>46149.375</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>46156.708333333299</v>
       </c>
       <c r="J10" t="s">
         <v>11</v>
       </c>
-      <c r="K10">
-        <v>90</v>
+      <c r="K10" s="2">
+        <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>11</v>
+        <v>125</v>
       </c>
       <c r="M10" t="s">
         <v>11</v>
@@ -1077,7 +1086,7 @@
         <v>38</v>
       </c>
       <c r="S10" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="T10" t="s">
         <v>11</v>
@@ -1117,17 +1126,17 @@
       <c r="G11" t="s">
         <v>11</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>46149.375</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>46156.708333333299</v>
       </c>
       <c r="J11" t="s">
         <v>11</v>
       </c>
-      <c r="K11">
-        <v>100</v>
+      <c r="K11" s="2">
+        <v>1</v>
       </c>
       <c r="L11" t="s">
         <v>125</v>
@@ -1148,7 +1157,7 @@
         <v>37</v>
       </c>
       <c r="R11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S11" t="s">
         <v>42</v>
@@ -1197,8 +1206,8 @@
       <c r="J12" t="s">
         <v>11</v>
       </c>
-      <c r="K12">
-        <v>100</v>
+      <c r="K12" s="2">
+        <v>1</v>
       </c>
       <c r="L12" t="s">
         <v>125</v>
@@ -1219,7 +1228,7 @@
         <v>37</v>
       </c>
       <c r="R12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S12" t="s">
         <v>42</v>
@@ -1262,17 +1271,17 @@
       <c r="G13" t="s">
         <v>11</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>46149.375</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>46156.708333333299</v>
       </c>
       <c r="J13" t="s">
         <v>11</v>
       </c>
-      <c r="K13">
-        <v>100</v>
+      <c r="K13" s="2">
+        <v>1</v>
       </c>
       <c r="L13" t="s">
         <v>125</v>
@@ -1293,7 +1302,7 @@
         <v>37</v>
       </c>
       <c r="R13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S13" t="s">
         <v>42</v>
@@ -1336,17 +1345,17 @@
       <c r="G14" t="s">
         <v>11</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>46149.375</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>46156.708333333299</v>
       </c>
       <c r="J14" t="s">
         <v>11</v>
       </c>
-      <c r="K14">
-        <v>100</v>
+      <c r="K14" s="2">
+        <v>1</v>
       </c>
       <c r="L14" t="s">
         <v>125</v>
@@ -1367,7 +1376,7 @@
         <v>37</v>
       </c>
       <c r="R14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S14" t="s">
         <v>42</v>
@@ -1410,17 +1419,17 @@
       <c r="G15" t="s">
         <v>11</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>46149.375</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>46156.708333333299</v>
       </c>
       <c r="J15" t="s">
         <v>11</v>
       </c>
-      <c r="K15">
-        <v>100</v>
+      <c r="K15" s="2">
+        <v>1</v>
       </c>
       <c r="L15" t="s">
         <v>125</v>
@@ -1441,7 +1450,7 @@
         <v>37</v>
       </c>
       <c r="R15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S15" t="s">
         <v>42</v>
@@ -1484,17 +1493,17 @@
       <c r="G16" t="s">
         <v>11</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>46149.375</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>46156.708333333299</v>
       </c>
       <c r="J16" t="s">
         <v>11</v>
       </c>
-      <c r="K16">
-        <v>100</v>
+      <c r="K16" s="2">
+        <v>1</v>
       </c>
       <c r="L16" t="s">
         <v>125</v>
@@ -1515,7 +1524,7 @@
         <v>37</v>
       </c>
       <c r="R16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="S16" t="s">
         <v>42</v>
@@ -1558,20 +1567,20 @@
       <c r="G17" t="s">
         <v>11</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>46149.375</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>46156.708333333299</v>
       </c>
       <c r="J17" t="s">
         <v>11</v>
       </c>
-      <c r="K17">
-        <v>0</v>
+      <c r="K17" s="2">
+        <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M17" t="s">
         <v>11</v>
@@ -1589,10 +1598,10 @@
         <v>37</v>
       </c>
       <c r="R17" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="S17" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="T17" t="s">
         <v>11</v>
@@ -1632,17 +1641,17 @@
       <c r="G18" t="s">
         <v>11</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>46149.375</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>46156.708333333299</v>
       </c>
       <c r="J18" t="s">
         <v>11</v>
       </c>
-      <c r="K18">
-        <v>100</v>
+      <c r="K18" s="2">
+        <v>1</v>
       </c>
       <c r="L18" t="s">
         <v>125</v>
@@ -1663,7 +1672,7 @@
         <v>37</v>
       </c>
       <c r="R18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="S18" t="s">
         <v>42</v>
@@ -1706,17 +1715,17 @@
       <c r="G19" t="s">
         <v>11</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>46149.375</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>46156.708333333299</v>
       </c>
       <c r="J19" t="s">
         <v>11</v>
       </c>
-      <c r="K19">
-        <v>100</v>
+      <c r="K19" s="2">
+        <v>1</v>
       </c>
       <c r="L19" t="s">
         <v>125</v>
@@ -1737,7 +1746,7 @@
         <v>37</v>
       </c>
       <c r="R19" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S19" t="s">
         <v>42</v>
@@ -1780,17 +1789,17 @@
       <c r="G20" t="s">
         <v>11</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>46149.375</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>46156.708333333299</v>
       </c>
       <c r="J20" t="s">
         <v>11</v>
       </c>
-      <c r="K20">
-        <v>100</v>
+      <c r="K20" s="2">
+        <v>1</v>
       </c>
       <c r="L20" t="s">
         <v>125</v>
@@ -1811,7 +1820,7 @@
         <v>37</v>
       </c>
       <c r="R20" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="S20" t="s">
         <v>42</v>
@@ -1854,17 +1863,17 @@
       <c r="G21" t="s">
         <v>11</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>46149.375</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>46156.708333333299</v>
       </c>
       <c r="J21" t="s">
         <v>11</v>
       </c>
-      <c r="K21">
-        <v>100</v>
+      <c r="K21" s="2">
+        <v>1</v>
       </c>
       <c r="L21" t="s">
         <v>125</v>
@@ -1885,7 +1894,7 @@
         <v>37</v>
       </c>
       <c r="R21" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="S21" t="s">
         <v>42</v>
@@ -1928,17 +1937,17 @@
       <c r="G22" t="s">
         <v>11</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>46149.375</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="1">
         <v>46156.708333333299</v>
       </c>
       <c r="J22" t="s">
         <v>11</v>
       </c>
-      <c r="K22">
-        <v>100</v>
+      <c r="K22" s="2">
+        <v>1</v>
       </c>
       <c r="L22" t="s">
         <v>125</v>
@@ -1959,7 +1968,7 @@
         <v>37</v>
       </c>
       <c r="R22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="S22" t="s">
         <v>42</v>
@@ -2011,11 +2020,11 @@
       <c r="J23" t="s">
         <v>11</v>
       </c>
-      <c r="K23">
-        <v>80</v>
+      <c r="K23" s="2">
+        <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>11</v>
+        <v>125</v>
       </c>
       <c r="M23" t="s">
         <v>11</v>
@@ -2033,10 +2042,10 @@
         <v>42</v>
       </c>
       <c r="R23" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="S23" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="T23" t="s">
         <v>11</v>
@@ -2085,8 +2094,8 @@
       <c r="J24" t="s">
         <v>11</v>
       </c>
-      <c r="K24">
-        <v>100</v>
+      <c r="K24" s="2">
+        <v>1</v>
       </c>
       <c r="L24" t="s">
         <v>125</v>
@@ -2107,7 +2116,7 @@
         <v>37</v>
       </c>
       <c r="R24" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="S24" t="s">
         <v>42</v>
@@ -2159,8 +2168,8 @@
       <c r="J25" t="s">
         <v>11</v>
       </c>
-      <c r="K25">
-        <v>100</v>
+      <c r="K25" s="2">
+        <v>1</v>
       </c>
       <c r="L25" t="s">
         <v>125</v>
@@ -2181,7 +2190,7 @@
         <v>37</v>
       </c>
       <c r="R25" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="S25" t="s">
         <v>42</v>
@@ -2233,8 +2242,8 @@
       <c r="J26" t="s">
         <v>11</v>
       </c>
-      <c r="K26">
-        <v>100</v>
+      <c r="K26" s="2">
+        <v>1</v>
       </c>
       <c r="L26" t="s">
         <v>125</v>
@@ -2255,7 +2264,7 @@
         <v>37</v>
       </c>
       <c r="R26" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="S26" t="s">
         <v>42</v>
@@ -2307,8 +2316,8 @@
       <c r="J27" t="s">
         <v>11</v>
       </c>
-      <c r="K27">
-        <v>100</v>
+      <c r="K27" s="2">
+        <v>1</v>
       </c>
       <c r="L27" t="s">
         <v>125</v>
@@ -2329,7 +2338,7 @@
         <v>37</v>
       </c>
       <c r="R27" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="S27" t="s">
         <v>42</v>
@@ -2381,11 +2390,11 @@
       <c r="J28" t="s">
         <v>11</v>
       </c>
-      <c r="K28">
-        <v>85</v>
+      <c r="K28" s="2">
+        <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>11</v>
+        <v>125</v>
       </c>
       <c r="M28" t="s">
         <v>11</v>
@@ -2403,10 +2412,10 @@
         <v>42</v>
       </c>
       <c r="R28" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="S28" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="T28" t="s">
         <v>11</v>
@@ -2455,8 +2464,8 @@
       <c r="J29" t="s">
         <v>11</v>
       </c>
-      <c r="K29">
-        <v>100</v>
+      <c r="K29" s="2">
+        <v>1</v>
       </c>
       <c r="L29" t="s">
         <v>125</v>
@@ -2477,7 +2486,7 @@
         <v>37</v>
       </c>
       <c r="R29" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="S29" t="s">
         <v>42</v>
@@ -2529,8 +2538,8 @@
       <c r="J30" t="s">
         <v>11</v>
       </c>
-      <c r="K30">
-        <v>100</v>
+      <c r="K30" s="2">
+        <v>1</v>
       </c>
       <c r="L30" t="s">
         <v>125</v>
@@ -2551,7 +2560,7 @@
         <v>37</v>
       </c>
       <c r="R30" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="S30" t="s">
         <v>42</v>
@@ -2603,8 +2612,8 @@
       <c r="J31" t="s">
         <v>11</v>
       </c>
-      <c r="K31">
-        <v>100</v>
+      <c r="K31" s="2">
+        <v>1</v>
       </c>
       <c r="L31" t="s">
         <v>125</v>
@@ -2625,7 +2634,7 @@
         <v>37</v>
       </c>
       <c r="R31" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="S31" t="s">
         <v>42</v>
@@ -2677,8 +2686,8 @@
       <c r="J32" t="s">
         <v>11</v>
       </c>
-      <c r="K32">
-        <v>100</v>
+      <c r="K32" s="2">
+        <v>1</v>
       </c>
       <c r="L32" t="s">
         <v>125</v>
@@ -2699,7 +2708,7 @@
         <v>37</v>
       </c>
       <c r="R32" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="S32" t="s">
         <v>42</v>
@@ -2751,8 +2760,8 @@
       <c r="J33" t="s">
         <v>11</v>
       </c>
-      <c r="K33">
-        <v>100</v>
+      <c r="K33" s="2">
+        <v>1</v>
       </c>
       <c r="L33" t="s">
         <v>125</v>
@@ -2773,7 +2782,7 @@
         <v>37</v>
       </c>
       <c r="R33" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="S33" t="s">
         <v>42</v>
@@ -2825,11 +2834,11 @@
       <c r="J34" t="s">
         <v>11</v>
       </c>
-      <c r="K34">
-        <v>50</v>
+      <c r="K34" s="2">
+        <v>1</v>
       </c>
       <c r="L34" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M34" t="s">
         <v>11</v>
@@ -2847,10 +2856,10 @@
         <v>37</v>
       </c>
       <c r="R34" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="S34" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="T34" t="s">
         <v>11</v>
@@ -2899,7 +2908,7 @@
       <c r="J35" t="s">
         <v>11</v>
       </c>
-      <c r="K35">
+      <c r="K35" s="2">
         <v>0</v>
       </c>
       <c r="L35" t="s">
@@ -2921,7 +2930,7 @@
         <v>37</v>
       </c>
       <c r="R35" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="S35" t="s">
         <v>11</v>
@@ -2973,8 +2982,8 @@
       <c r="J36" t="s">
         <v>11</v>
       </c>
-      <c r="K36">
-        <v>100</v>
+      <c r="K36" s="2">
+        <v>1</v>
       </c>
       <c r="L36" t="s">
         <v>125</v>
@@ -2995,7 +3004,7 @@
         <v>37</v>
       </c>
       <c r="R36" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="S36" t="s">
         <v>42</v>
@@ -3047,8 +3056,8 @@
       <c r="J37" t="s">
         <v>11</v>
       </c>
-      <c r="K37">
-        <v>100</v>
+      <c r="K37" s="2">
+        <v>1</v>
       </c>
       <c r="L37" t="s">
         <v>125</v>
@@ -3069,7 +3078,7 @@
         <v>37</v>
       </c>
       <c r="R37" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="S37" t="s">
         <v>42</v>
@@ -3121,7 +3130,7 @@
       <c r="J38" t="s">
         <v>11</v>
       </c>
-      <c r="K38">
+      <c r="K38" s="2">
         <v>0</v>
       </c>
       <c r="L38" t="s">
@@ -3186,20 +3195,20 @@
       <c r="G39" t="s">
         <v>11</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="1">
         <v>46148.375</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="1">
         <v>46150.708333333299</v>
       </c>
       <c r="J39" t="s">
         <v>11</v>
       </c>
-      <c r="K39">
-        <v>70</v>
+      <c r="K39" s="2">
+        <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>11</v>
+        <v>125</v>
       </c>
       <c r="M39" t="s">
         <v>11</v>
@@ -3217,10 +3226,10 @@
         <v>37</v>
       </c>
       <c r="R39" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="S39" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="T39" t="s">
         <v>11</v>
@@ -3260,20 +3269,20 @@
       <c r="G40" t="s">
         <v>11</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="1">
         <v>46148.375</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="1">
         <v>46150.708333333299</v>
       </c>
       <c r="J40" t="s">
         <v>11</v>
       </c>
-      <c r="K40">
-        <v>0</v>
+      <c r="K40" s="2">
+        <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M40" t="s">
         <v>11</v>
@@ -3291,10 +3300,10 @@
         <v>37</v>
       </c>
       <c r="R40" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="S40" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="T40" t="s">
         <v>11</v>
@@ -3334,20 +3343,20 @@
       <c r="G41" t="s">
         <v>11</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="1">
         <v>46148.375</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="1">
         <v>46150.708333333299</v>
       </c>
       <c r="J41" t="s">
         <v>11</v>
       </c>
-      <c r="K41">
-        <v>50</v>
+      <c r="K41" s="2">
+        <v>1</v>
       </c>
       <c r="L41" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M41" t="s">
         <v>11</v>
@@ -3365,10 +3374,10 @@
         <v>37</v>
       </c>
       <c r="R41" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="S41" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="T41" t="s">
         <v>11</v>
@@ -3408,20 +3417,20 @@
       <c r="G42" t="s">
         <v>11</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="1">
         <v>46148.375</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="1">
         <v>46150.708333333299</v>
       </c>
       <c r="J42" t="s">
         <v>11</v>
       </c>
-      <c r="K42">
-        <v>50</v>
+      <c r="K42" s="2">
+        <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M42" t="s">
         <v>11</v>
@@ -3439,10 +3448,10 @@
         <v>37</v>
       </c>
       <c r="R42" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="S42" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="T42" t="s">
         <v>11</v>
@@ -3482,20 +3491,20 @@
       <c r="G43" t="s">
         <v>11</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="1">
         <v>46148.375</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="1">
         <v>46150.708333333299</v>
       </c>
       <c r="J43" t="s">
         <v>11</v>
       </c>
-      <c r="K43">
-        <v>50</v>
+      <c r="K43" s="2">
+        <v>1</v>
       </c>
       <c r="L43" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M43" t="s">
         <v>11</v>
@@ -3513,10 +3522,10 @@
         <v>37</v>
       </c>
       <c r="R43" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="S43" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="T43" t="s">
         <v>11</v>
@@ -3556,20 +3565,20 @@
       <c r="G44" t="s">
         <v>11</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="1">
         <v>46148.375</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="1">
         <v>46150.708333333299</v>
       </c>
       <c r="J44" t="s">
         <v>11</v>
       </c>
-      <c r="K44">
-        <v>0</v>
+      <c r="K44" s="2">
+        <v>1</v>
       </c>
       <c r="L44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M44" t="s">
         <v>11</v>
@@ -3587,10 +3596,10 @@
         <v>37</v>
       </c>
       <c r="R44" t="s">
-        <v>11</v>
+        <v>157</v>
       </c>
       <c r="S44" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="T44" t="s">
         <v>11</v>
@@ -3630,17 +3639,17 @@
       <c r="G45" t="s">
         <v>11</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="1">
         <v>46148.375</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="1">
         <v>46150.708333333299</v>
       </c>
       <c r="J45" t="s">
         <v>11</v>
       </c>
-      <c r="K45">
-        <v>100</v>
+      <c r="K45" s="2">
+        <v>1</v>
       </c>
       <c r="L45" t="s">
         <v>125</v>
@@ -3661,7 +3670,7 @@
         <v>37</v>
       </c>
       <c r="R45" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="S45" t="s">
         <v>42</v>
@@ -3704,16 +3713,16 @@
       <c r="G46" t="s">
         <v>11</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="1">
         <v>46148.375</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="1">
         <v>46150.708333333299</v>
       </c>
       <c r="J46" t="s">
         <v>11</v>
       </c>
-      <c r="K46">
+      <c r="K46" s="2">
         <v>0</v>
       </c>
       <c r="L46" t="s">
@@ -3778,17 +3787,17 @@
       <c r="G47" t="s">
         <v>11</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="1">
         <v>46148.375</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="1">
         <v>46148.708333333299</v>
       </c>
       <c r="J47" t="s">
         <v>11</v>
       </c>
-      <c r="K47">
-        <v>100</v>
+      <c r="K47" s="2">
+        <v>1</v>
       </c>
       <c r="L47" t="s">
         <v>11</v>
@@ -3852,17 +3861,17 @@
       <c r="G48" t="s">
         <v>11</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="1">
         <v>46148.375</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="1">
         <v>46148.708333333299</v>
       </c>
       <c r="J48" t="s">
         <v>11</v>
       </c>
-      <c r="K48">
-        <v>100</v>
+      <c r="K48" s="2">
+        <v>1</v>
       </c>
       <c r="L48" t="s">
         <v>125</v>
@@ -3883,7 +3892,7 @@
         <v>37</v>
       </c>
       <c r="R48" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="S48" t="s">
         <v>42</v>
@@ -3935,8 +3944,8 @@
       <c r="J49" t="s">
         <v>11</v>
       </c>
-      <c r="K49">
-        <v>100</v>
+      <c r="K49" s="2">
+        <v>1</v>
       </c>
       <c r="L49" t="s">
         <v>125</v>
@@ -3957,7 +3966,7 @@
         <v>37</v>
       </c>
       <c r="R49" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="S49" t="s">
         <v>42</v>
@@ -4009,8 +4018,8 @@
       <c r="J50" t="s">
         <v>11</v>
       </c>
-      <c r="K50">
-        <v>100</v>
+      <c r="K50" s="2">
+        <v>1</v>
       </c>
       <c r="L50" t="s">
         <v>125</v>
@@ -4031,7 +4040,7 @@
         <v>37</v>
       </c>
       <c r="R50" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="S50" t="s">
         <v>42</v>
@@ -4083,8 +4092,8 @@
       <c r="J51" t="s">
         <v>11</v>
       </c>
-      <c r="K51">
-        <v>100</v>
+      <c r="K51" s="2">
+        <v>1</v>
       </c>
       <c r="L51" t="s">
         <v>125</v>
@@ -4105,7 +4114,7 @@
         <v>37</v>
       </c>
       <c r="R51" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="S51" t="s">
         <v>42</v>
@@ -4129,7 +4138,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:X10 A23:Q23 A11:K11 M11:Q11 A12:K12 M12:Q12 A13:K13 M13:Q13 A14:K14 M14:Q14 A15:K15 M15:Q15 A16:K16 M16:Q16 A17:K17 M17:Q17 A18:K18 M18:Q18 A19:K19 M19:Q19 A20:K20 M20:Q20 A21:K21 M21:Q21 A22:K22 M22:Q22 A28:Q28 A24:K24 M24:Q24 A25:K25 M25:Q25 A26:K26 M26:Q26 A27:K27 M27:Q27 A39:Q39 A29:K29 M29:Q29 A30:K30 M30:Q30 A31:K31 M31:Q31 A32:K32 M32:Q32 A33:K33 M33:Q33 A34:K34 M34:Q34 A35:K35 M35:Q35 A36:K36 M36:Q36 A37:K37 M37:Q37 A38:K38 M38:X38 A47:X47 A40:K40 M40:Q40 A41:K41 M41:Q41 A42:K42 M42:Q42 A43:K43 M43:Q43 A44:K44 M44:X44 A45:K45 M45:Q45 A46:K46 M46:X46 A51:K51 A48:K48 M48:Q48 A49:K49 M49:Q49 A50:K50 M50:Q50 M51:Q51 S11:X11 S12:X12 S13:X13 S14:X14 S15:X15 S16:X16 S17:X17 S18:X18 S19:X19 S20:X20 S21:X21 S22:X22 S23:X23 S24:X24 S25:X25 S26:X26 S27:X27 S28:X28 S29:X29 S30:X30 S31:X31 S32:X32 S33:X33 S34:X34 S35:X35 S36:X36 S37:X37 S39:X39 S40:X40 S41:X41 S42:X42 S43:X43 S45:X45 S48:X48 S49:X49 S50:X50 S51:X51" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:X5 A23:J23 A11:J11 M11:Q11 A12:J12 M12:Q12 A13:J13 M13:Q13 A14:J14 M14:Q14 A15:J15 M15:Q15 A16:J16 M16:Q16 A17:J17 M17:Q17 A18:J18 M18:Q18 A19:J19 M19:Q19 A20:J20 M20:Q20 A21:J21 M21:Q21 A22:J22 M22:Q22 A28:J28 A24:J24 M24:Q24 A25:J25 M25:Q25 A26:J26 M26:Q26 A27:J27 M27:Q27 A39:J39 A29:J29 M29:Q29 A30:J30 M30:Q30 A31:J31 M31:Q31 A32:J32 M32:Q32 A33:J33 M33:Q33 A34:J34 M34:Q34 A35:K35 M35:Q35 A36:J36 M36:Q36 A37:J37 M37:Q37 A38:K38 M38:X38 A47:J47 A40:J40 M40:Q40 A41:J41 M41:Q41 A42:J42 M42:Q42 A43:J43 M43:Q43 A44:J44 M44:Q44 A45:J45 M45:Q45 A46:K46 M46:X46 A51:J51 A48:J48 M48:Q48 A49:J49 M49:Q49 A50:J50 M50:Q50 M51:Q51 S11:X11 S12:X12 S13:X13 S14:X14 S15:X15 S16:X16 T17:X17 S18:X18 S19:X19 S20:X20 S21:X21 S22:X22 T23:X23 S24:X24 S25:X25 S26:X26 S27:X27 T28:X28 S29:X29 S30:X30 S31:X31 S32:X32 S33:X33 T34:X34 S35:X35 S36:X36 S37:X37 T39:X39 T40:X40 T41:X41 T42:X42 T43:X43 S45:X45 S48:X48 S49:X49 S50:X50 S51:X51 A7:X9 A6 C6:X6 M23:Q23 M28:Q28 M39:Q39 T44:X44 A10:J10 M10:R10 L47:X47 T10:X10" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Robot Monitoring.xlsx
+++ b/Robot Monitoring.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\xampp\htdocs\robot_dashboard\robot-navigasi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\robot_dashboard\robot-navigasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9B39D1-B592-4420-BD2A-650409B07B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8D08BC-E6DA-4EBC-A423-463731C2CA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="166">
   <si>
     <t>Project name</t>
   </si>
@@ -52,9 +52,6 @@
     <t>Exported on</t>
   </si>
   <si>
-    <t>Thu May 07 2026 15:04:15 GMT+0700 (Indochina Time)</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -512,6 +509,15 @@
   </si>
   <si>
     <t>Logbook menangkap semua event termasuk collision detection, proximity alerts, dan obstacle events</t>
+  </si>
+  <si>
+    <t>Memerlukan API Email</t>
+  </si>
+  <si>
+    <t>Sudah diimplementasikan di index.php</t>
+  </si>
+  <si>
+    <t>Thu May 07 2026 15:04:15 GMT+0700 (Indonesia Time)</t>
   </si>
 </sst>
 </file>
@@ -550,10 +556,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -892,6 +901,7 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5" customWidth="1"/>
     <col min="8" max="9" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -939,7 +949,7 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>0.95</v>
       </c>
     </row>
@@ -948,86 +958,86 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>14</v>
-      </c>
-      <c r="D9" t="s">
-        <v>15</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
       </c>
       <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
         <v>16</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>17</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>18</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>19</v>
-      </c>
-      <c r="J9" t="s">
-        <v>20</v>
       </c>
       <c r="K9" t="s">
         <v>8</v>
       </c>
       <c r="L9" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" t="s">
         <v>21</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>22</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>23</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>24</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>25</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
+        <v>16</v>
+      </c>
+      <c r="S9" t="s">
         <v>26</v>
       </c>
-      <c r="R9" t="s">
-        <v>17</v>
-      </c>
-      <c r="S9" t="s">
+      <c r="T9" t="s">
         <v>27</v>
       </c>
-      <c r="T9" t="s">
+      <c r="U9" t="s">
         <v>28</v>
       </c>
-      <c r="U9" t="s">
+      <c r="V9" t="s">
         <v>29</v>
       </c>
-      <c r="V9" t="s">
+      <c r="W9" t="s">
         <v>30</v>
       </c>
-      <c r="W9" t="s">
+      <c r="X9" t="s">
         <v>31</v>
-      </c>
-      <c r="X9" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -1035,22 +1045,22 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
         <v>33</v>
       </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
       <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
         <v>35</v>
       </c>
-      <c r="E10" t="s">
-        <v>36</v>
-      </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H10" s="1">
         <v>46149.375</v>
@@ -1059,49 +1069,49 @@
         <v>46156.708333333299</v>
       </c>
       <c r="J10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="s">
+        <v>36</v>
+      </c>
+      <c r="R10" t="s">
         <v>37</v>
       </c>
-      <c r="R10" t="s">
-        <v>38</v>
-      </c>
       <c r="S10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -1109,22 +1119,22 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
         <v>40</v>
       </c>
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
       <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
         <v>35</v>
       </c>
-      <c r="E11" t="s">
-        <v>36</v>
-      </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H11" s="1">
         <v>46149.375</v>
@@ -1133,49 +1143,49 @@
         <v>46156.708333333299</v>
       </c>
       <c r="J11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S11" t="s">
+        <v>41</v>
+      </c>
+      <c r="T11" t="s">
+        <v>10</v>
+      </c>
+      <c r="U11" t="s">
+        <v>10</v>
+      </c>
+      <c r="V11" t="s">
+        <v>38</v>
+      </c>
+      <c r="W11" t="s">
         <v>42</v>
       </c>
-      <c r="T11" t="s">
-        <v>11</v>
-      </c>
-      <c r="U11" t="s">
-        <v>11</v>
-      </c>
-      <c r="V11" t="s">
-        <v>39</v>
-      </c>
-      <c r="W11" t="s">
-        <v>43</v>
-      </c>
       <c r="X11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
@@ -1183,70 +1193,70 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
         <v>44</v>
       </c>
-      <c r="C12" t="s">
-        <v>45</v>
-      </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>46149.375</v>
+      </c>
+      <c r="I12" s="1">
+        <v>46156.708333333299</v>
       </c>
       <c r="J12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K12" s="2">
         <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S12" t="s">
+        <v>41</v>
+      </c>
+      <c r="T12" t="s">
+        <v>10</v>
+      </c>
+      <c r="U12" t="s">
+        <v>10</v>
+      </c>
+      <c r="V12" t="s">
+        <v>38</v>
+      </c>
+      <c r="W12" t="s">
         <v>42</v>
       </c>
-      <c r="T12" t="s">
-        <v>11</v>
-      </c>
-      <c r="U12" t="s">
-        <v>11</v>
-      </c>
-      <c r="V12" t="s">
-        <v>39</v>
-      </c>
-      <c r="W12" t="s">
-        <v>43</v>
-      </c>
       <c r="X12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -1254,22 +1264,22 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
         <v>46</v>
       </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
       <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
         <v>35</v>
       </c>
-      <c r="E13" t="s">
-        <v>36</v>
-      </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H13" s="1">
         <v>46149.375</v>
@@ -1278,49 +1288,49 @@
         <v>46156.708333333299</v>
       </c>
       <c r="J13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K13" s="2">
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S13" t="s">
+        <v>41</v>
+      </c>
+      <c r="T13" t="s">
+        <v>10</v>
+      </c>
+      <c r="U13" t="s">
+        <v>10</v>
+      </c>
+      <c r="V13" t="s">
+        <v>38</v>
+      </c>
+      <c r="W13" t="s">
         <v>42</v>
       </c>
-      <c r="T13" t="s">
-        <v>11</v>
-      </c>
-      <c r="U13" t="s">
-        <v>11</v>
-      </c>
-      <c r="V13" t="s">
-        <v>39</v>
-      </c>
-      <c r="W13" t="s">
-        <v>43</v>
-      </c>
       <c r="X13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -1328,22 +1338,22 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
         <v>48</v>
       </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
       <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
         <v>35</v>
       </c>
-      <c r="E14" t="s">
-        <v>36</v>
-      </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H14" s="1">
         <v>46149.375</v>
@@ -1352,49 +1362,49 @@
         <v>46156.708333333299</v>
       </c>
       <c r="J14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K14" s="2">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S14" t="s">
+        <v>41</v>
+      </c>
+      <c r="T14" t="s">
+        <v>10</v>
+      </c>
+      <c r="U14" t="s">
+        <v>10</v>
+      </c>
+      <c r="V14" t="s">
+        <v>38</v>
+      </c>
+      <c r="W14" t="s">
         <v>42</v>
       </c>
-      <c r="T14" t="s">
-        <v>11</v>
-      </c>
-      <c r="U14" t="s">
-        <v>11</v>
-      </c>
-      <c r="V14" t="s">
-        <v>39</v>
-      </c>
-      <c r="W14" t="s">
-        <v>43</v>
-      </c>
       <c r="X14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -1402,22 +1412,22 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
         <v>50</v>
       </c>
-      <c r="C15" t="s">
-        <v>51</v>
-      </c>
       <c r="D15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" t="s">
         <v>35</v>
       </c>
-      <c r="E15" t="s">
-        <v>36</v>
-      </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H15" s="1">
         <v>46149.375</v>
@@ -1426,49 +1436,49 @@
         <v>46156.708333333299</v>
       </c>
       <c r="J15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K15" s="2">
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S15" t="s">
+        <v>41</v>
+      </c>
+      <c r="T15" t="s">
+        <v>10</v>
+      </c>
+      <c r="U15" t="s">
+        <v>10</v>
+      </c>
+      <c r="V15" t="s">
+        <v>38</v>
+      </c>
+      <c r="W15" t="s">
         <v>42</v>
       </c>
-      <c r="T15" t="s">
-        <v>11</v>
-      </c>
-      <c r="U15" t="s">
-        <v>11</v>
-      </c>
-      <c r="V15" t="s">
-        <v>39</v>
-      </c>
-      <c r="W15" t="s">
-        <v>43</v>
-      </c>
       <c r="X15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
@@ -1476,22 +1486,22 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" t="s">
         <v>52</v>
       </c>
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
       <c r="D16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" t="s">
         <v>35</v>
       </c>
-      <c r="E16" t="s">
-        <v>36</v>
-      </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H16" s="1">
         <v>46149.375</v>
@@ -1500,49 +1510,49 @@
         <v>46156.708333333299</v>
       </c>
       <c r="J16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K16" s="2">
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S16" t="s">
+        <v>41</v>
+      </c>
+      <c r="T16" t="s">
+        <v>10</v>
+      </c>
+      <c r="U16" t="s">
+        <v>10</v>
+      </c>
+      <c r="V16" t="s">
+        <v>38</v>
+      </c>
+      <c r="W16" t="s">
         <v>42</v>
       </c>
-      <c r="T16" t="s">
-        <v>11</v>
-      </c>
-      <c r="U16" t="s">
-        <v>11</v>
-      </c>
-      <c r="V16" t="s">
-        <v>39</v>
-      </c>
-      <c r="W16" t="s">
-        <v>43</v>
-      </c>
       <c r="X16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
@@ -1550,22 +1560,22 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s">
         <v>54</v>
       </c>
-      <c r="C17" t="s">
-        <v>55</v>
-      </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H17" s="1">
         <v>46149.375</v>
@@ -1574,49 +1584,49 @@
         <v>46156.708333333299</v>
       </c>
       <c r="J17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K17" s="2">
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="S17" t="s">
+        <v>41</v>
+      </c>
+      <c r="T17" t="s">
+        <v>10</v>
+      </c>
+      <c r="U17" t="s">
+        <v>10</v>
+      </c>
+      <c r="V17" t="s">
+        <v>38</v>
+      </c>
+      <c r="W17" t="s">
         <v>42</v>
       </c>
-      <c r="T17" t="s">
-        <v>11</v>
-      </c>
-      <c r="U17" t="s">
-        <v>11</v>
-      </c>
-      <c r="V17" t="s">
-        <v>39</v>
-      </c>
-      <c r="W17" t="s">
-        <v>43</v>
-      </c>
       <c r="X17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
@@ -1624,22 +1634,22 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
         <v>56</v>
       </c>
-      <c r="C18" t="s">
-        <v>57</v>
-      </c>
       <c r="D18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" t="s">
         <v>35</v>
       </c>
-      <c r="E18" t="s">
-        <v>36</v>
-      </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H18" s="1">
         <v>46149.375</v>
@@ -1648,49 +1658,49 @@
         <v>46156.708333333299</v>
       </c>
       <c r="J18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K18" s="2">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="S18" t="s">
+        <v>41</v>
+      </c>
+      <c r="T18" t="s">
+        <v>10</v>
+      </c>
+      <c r="U18" t="s">
+        <v>10</v>
+      </c>
+      <c r="V18" t="s">
+        <v>38</v>
+      </c>
+      <c r="W18" t="s">
         <v>42</v>
       </c>
-      <c r="T18" t="s">
-        <v>11</v>
-      </c>
-      <c r="U18" t="s">
-        <v>11</v>
-      </c>
-      <c r="V18" t="s">
-        <v>39</v>
-      </c>
-      <c r="W18" t="s">
-        <v>43</v>
-      </c>
       <c r="X18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
@@ -1698,22 +1708,22 @@
         <v>10</v>
       </c>
       <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
         <v>58</v>
       </c>
-      <c r="C19" t="s">
-        <v>59</v>
-      </c>
       <c r="D19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" t="s">
         <v>35</v>
       </c>
-      <c r="E19" t="s">
-        <v>36</v>
-      </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H19" s="1">
         <v>46149.375</v>
@@ -1722,49 +1732,49 @@
         <v>46156.708333333299</v>
       </c>
       <c r="J19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K19" s="2">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S19" t="s">
+        <v>41</v>
+      </c>
+      <c r="T19" t="s">
+        <v>10</v>
+      </c>
+      <c r="U19" t="s">
+        <v>10</v>
+      </c>
+      <c r="V19" t="s">
+        <v>38</v>
+      </c>
+      <c r="W19" t="s">
         <v>42</v>
       </c>
-      <c r="T19" t="s">
-        <v>11</v>
-      </c>
-      <c r="U19" t="s">
-        <v>11</v>
-      </c>
-      <c r="V19" t="s">
-        <v>39</v>
-      </c>
-      <c r="W19" t="s">
-        <v>43</v>
-      </c>
       <c r="X19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
@@ -1772,22 +1782,22 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
         <v>60</v>
       </c>
-      <c r="C20" t="s">
-        <v>61</v>
-      </c>
       <c r="D20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" t="s">
         <v>35</v>
       </c>
-      <c r="E20" t="s">
-        <v>36</v>
-      </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H20" s="1">
         <v>46149.375</v>
@@ -1796,49 +1806,49 @@
         <v>46156.708333333299</v>
       </c>
       <c r="J20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K20" s="2">
         <v>1</v>
       </c>
       <c r="L20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S20" t="s">
+        <v>41</v>
+      </c>
+      <c r="T20" t="s">
+        <v>10</v>
+      </c>
+      <c r="U20" t="s">
+        <v>10</v>
+      </c>
+      <c r="V20" t="s">
+        <v>38</v>
+      </c>
+      <c r="W20" t="s">
         <v>42</v>
       </c>
-      <c r="T20" t="s">
-        <v>11</v>
-      </c>
-      <c r="U20" t="s">
-        <v>11</v>
-      </c>
-      <c r="V20" t="s">
-        <v>39</v>
-      </c>
-      <c r="W20" t="s">
-        <v>43</v>
-      </c>
       <c r="X20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
@@ -1846,22 +1856,22 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s">
         <v>62</v>
       </c>
-      <c r="C21" t="s">
-        <v>63</v>
-      </c>
       <c r="D21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" t="s">
         <v>35</v>
       </c>
-      <c r="E21" t="s">
-        <v>36</v>
-      </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H21" s="1">
         <v>46149.375</v>
@@ -1870,49 +1880,49 @@
         <v>46156.708333333299</v>
       </c>
       <c r="J21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K21" s="2">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S21" t="s">
+        <v>41</v>
+      </c>
+      <c r="T21" t="s">
+        <v>10</v>
+      </c>
+      <c r="U21" t="s">
+        <v>10</v>
+      </c>
+      <c r="V21" t="s">
+        <v>38</v>
+      </c>
+      <c r="W21" t="s">
         <v>42</v>
       </c>
-      <c r="T21" t="s">
-        <v>11</v>
-      </c>
-      <c r="U21" t="s">
-        <v>11</v>
-      </c>
-      <c r="V21" t="s">
-        <v>39</v>
-      </c>
-      <c r="W21" t="s">
-        <v>43</v>
-      </c>
       <c r="X21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
@@ -1920,22 +1930,22 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
         <v>64</v>
       </c>
-      <c r="C22" t="s">
-        <v>65</v>
-      </c>
       <c r="D22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" t="s">
         <v>35</v>
       </c>
-      <c r="E22" t="s">
-        <v>36</v>
-      </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H22" s="1">
         <v>46149.375</v>
@@ -1944,49 +1954,49 @@
         <v>46156.708333333299</v>
       </c>
       <c r="J22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K22" s="2">
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S22" t="s">
+        <v>41</v>
+      </c>
+      <c r="T22" t="s">
+        <v>10</v>
+      </c>
+      <c r="U22" t="s">
+        <v>10</v>
+      </c>
+      <c r="V22" t="s">
+        <v>38</v>
+      </c>
+      <c r="W22" t="s">
         <v>42</v>
       </c>
-      <c r="T22" t="s">
-        <v>11</v>
-      </c>
-      <c r="U22" t="s">
-        <v>11</v>
-      </c>
-      <c r="V22" t="s">
-        <v>39</v>
-      </c>
-      <c r="W22" t="s">
-        <v>43</v>
-      </c>
       <c r="X22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
@@ -1994,73 +2004,73 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" t="s">
         <v>66</v>
       </c>
-      <c r="C23" t="s">
-        <v>67</v>
-      </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K23" s="2">
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="S23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
@@ -2068,73 +2078,73 @@
         <v>15</v>
       </c>
       <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" t="s">
         <v>68</v>
       </c>
-      <c r="C24" t="s">
-        <v>69</v>
-      </c>
       <c r="D24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K24" s="2">
         <v>1</v>
       </c>
       <c r="L24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S24" t="s">
+        <v>41</v>
+      </c>
+      <c r="T24" t="s">
+        <v>10</v>
+      </c>
+      <c r="U24" t="s">
+        <v>10</v>
+      </c>
+      <c r="V24" t="s">
+        <v>38</v>
+      </c>
+      <c r="W24" t="s">
         <v>42</v>
       </c>
-      <c r="T24" t="s">
-        <v>11</v>
-      </c>
-      <c r="U24" t="s">
-        <v>11</v>
-      </c>
-      <c r="V24" t="s">
-        <v>39</v>
-      </c>
-      <c r="W24" t="s">
-        <v>43</v>
-      </c>
       <c r="X24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
@@ -2142,73 +2152,73 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" t="s">
         <v>70</v>
       </c>
-      <c r="C25" t="s">
-        <v>71</v>
-      </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K25" s="2">
         <v>1</v>
       </c>
       <c r="L25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S25" t="s">
+        <v>41</v>
+      </c>
+      <c r="T25" t="s">
+        <v>10</v>
+      </c>
+      <c r="U25" t="s">
+        <v>10</v>
+      </c>
+      <c r="V25" t="s">
+        <v>38</v>
+      </c>
+      <c r="W25" t="s">
         <v>42</v>
       </c>
-      <c r="T25" t="s">
-        <v>11</v>
-      </c>
-      <c r="U25" t="s">
-        <v>11</v>
-      </c>
-      <c r="V25" t="s">
-        <v>39</v>
-      </c>
-      <c r="W25" t="s">
-        <v>43</v>
-      </c>
       <c r="X25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
@@ -2216,73 +2226,73 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" t="s">
         <v>72</v>
       </c>
-      <c r="C26" t="s">
-        <v>73</v>
-      </c>
       <c r="D26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K26" s="2">
         <v>1</v>
       </c>
       <c r="L26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S26" t="s">
+        <v>41</v>
+      </c>
+      <c r="T26" t="s">
+        <v>10</v>
+      </c>
+      <c r="U26" t="s">
+        <v>10</v>
+      </c>
+      <c r="V26" t="s">
+        <v>38</v>
+      </c>
+      <c r="W26" t="s">
         <v>42</v>
       </c>
-      <c r="T26" t="s">
-        <v>11</v>
-      </c>
-      <c r="U26" t="s">
-        <v>11</v>
-      </c>
-      <c r="V26" t="s">
-        <v>39</v>
-      </c>
-      <c r="W26" t="s">
-        <v>43</v>
-      </c>
       <c r="X26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
@@ -2290,73 +2300,73 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" t="s">
         <v>74</v>
       </c>
-      <c r="C27" t="s">
-        <v>75</v>
-      </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K27" s="2">
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="S27" t="s">
+        <v>41</v>
+      </c>
+      <c r="T27" t="s">
+        <v>10</v>
+      </c>
+      <c r="U27" t="s">
+        <v>10</v>
+      </c>
+      <c r="V27" t="s">
+        <v>38</v>
+      </c>
+      <c r="W27" t="s">
         <v>42</v>
       </c>
-      <c r="T27" t="s">
-        <v>11</v>
-      </c>
-      <c r="U27" t="s">
-        <v>11</v>
-      </c>
-      <c r="V27" t="s">
-        <v>39</v>
-      </c>
-      <c r="W27" t="s">
-        <v>43</v>
-      </c>
       <c r="X27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
@@ -2364,73 +2374,73 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" t="s">
         <v>76</v>
       </c>
-      <c r="C28" t="s">
-        <v>77</v>
-      </c>
       <c r="D28" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K28" s="2">
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R28" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="S28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
@@ -2438,73 +2448,73 @@
         <v>20</v>
       </c>
       <c r="B29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" t="s">
         <v>78</v>
       </c>
-      <c r="C29" t="s">
-        <v>79</v>
-      </c>
       <c r="D29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K29" s="2">
         <v>1</v>
       </c>
       <c r="L29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="S29" t="s">
+        <v>41</v>
+      </c>
+      <c r="T29" t="s">
+        <v>10</v>
+      </c>
+      <c r="U29" t="s">
+        <v>10</v>
+      </c>
+      <c r="V29" t="s">
+        <v>38</v>
+      </c>
+      <c r="W29" t="s">
         <v>42</v>
       </c>
-      <c r="T29" t="s">
-        <v>11</v>
-      </c>
-      <c r="U29" t="s">
-        <v>11</v>
-      </c>
-      <c r="V29" t="s">
-        <v>39</v>
-      </c>
-      <c r="W29" t="s">
-        <v>43</v>
-      </c>
       <c r="X29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
@@ -2512,73 +2522,73 @@
         <v>21</v>
       </c>
       <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" t="s">
         <v>80</v>
       </c>
-      <c r="C30" t="s">
-        <v>81</v>
-      </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K30" s="2">
         <v>1</v>
       </c>
       <c r="L30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S30" t="s">
+        <v>41</v>
+      </c>
+      <c r="T30" t="s">
+        <v>10</v>
+      </c>
+      <c r="U30" t="s">
+        <v>10</v>
+      </c>
+      <c r="V30" t="s">
+        <v>38</v>
+      </c>
+      <c r="W30" t="s">
         <v>42</v>
       </c>
-      <c r="T30" t="s">
-        <v>11</v>
-      </c>
-      <c r="U30" t="s">
-        <v>11</v>
-      </c>
-      <c r="V30" t="s">
-        <v>39</v>
-      </c>
-      <c r="W30" t="s">
-        <v>43</v>
-      </c>
       <c r="X30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
@@ -2586,73 +2596,73 @@
         <v>22</v>
       </c>
       <c r="B31" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" t="s">
         <v>82</v>
       </c>
-      <c r="C31" t="s">
-        <v>83</v>
-      </c>
       <c r="D31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K31" s="2">
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="S31" t="s">
+        <v>41</v>
+      </c>
+      <c r="T31" t="s">
+        <v>10</v>
+      </c>
+      <c r="U31" t="s">
+        <v>10</v>
+      </c>
+      <c r="V31" t="s">
+        <v>38</v>
+      </c>
+      <c r="W31" t="s">
         <v>42</v>
       </c>
-      <c r="T31" t="s">
-        <v>11</v>
-      </c>
-      <c r="U31" t="s">
-        <v>11</v>
-      </c>
-      <c r="V31" t="s">
-        <v>39</v>
-      </c>
-      <c r="W31" t="s">
-        <v>43</v>
-      </c>
       <c r="X31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
@@ -2660,73 +2670,73 @@
         <v>23</v>
       </c>
       <c r="B32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" t="s">
         <v>84</v>
       </c>
-      <c r="C32" t="s">
-        <v>85</v>
-      </c>
       <c r="D32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K32" s="2">
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R32" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S32" t="s">
+        <v>41</v>
+      </c>
+      <c r="T32" t="s">
+        <v>10</v>
+      </c>
+      <c r="U32" t="s">
+        <v>10</v>
+      </c>
+      <c r="V32" t="s">
+        <v>38</v>
+      </c>
+      <c r="W32" t="s">
         <v>42</v>
       </c>
-      <c r="T32" t="s">
-        <v>11</v>
-      </c>
-      <c r="U32" t="s">
-        <v>11</v>
-      </c>
-      <c r="V32" t="s">
-        <v>39</v>
-      </c>
-      <c r="W32" t="s">
-        <v>43</v>
-      </c>
       <c r="X32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
@@ -2734,73 +2744,73 @@
         <v>24</v>
       </c>
       <c r="B33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" t="s">
         <v>86</v>
       </c>
-      <c r="C33" t="s">
-        <v>87</v>
-      </c>
       <c r="D33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K33" s="2">
         <v>1</v>
       </c>
       <c r="L33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="S33" t="s">
+        <v>41</v>
+      </c>
+      <c r="T33" t="s">
+        <v>10</v>
+      </c>
+      <c r="U33" t="s">
+        <v>10</v>
+      </c>
+      <c r="V33" t="s">
+        <v>38</v>
+      </c>
+      <c r="W33" t="s">
         <v>42</v>
       </c>
-      <c r="T33" t="s">
-        <v>11</v>
-      </c>
-      <c r="U33" t="s">
-        <v>11</v>
-      </c>
-      <c r="V33" t="s">
-        <v>39</v>
-      </c>
-      <c r="W33" t="s">
-        <v>43</v>
-      </c>
       <c r="X33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
@@ -2808,73 +2818,73 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" t="s">
         <v>88</v>
       </c>
-      <c r="C34" t="s">
-        <v>89</v>
-      </c>
       <c r="D34" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K34" s="2">
         <v>1</v>
       </c>
       <c r="L34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R34" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="S34" t="s">
+        <v>41</v>
+      </c>
+      <c r="T34" t="s">
+        <v>10</v>
+      </c>
+      <c r="U34" t="s">
+        <v>10</v>
+      </c>
+      <c r="V34" t="s">
+        <v>38</v>
+      </c>
+      <c r="W34" t="s">
         <v>42</v>
       </c>
-      <c r="T34" t="s">
-        <v>11</v>
-      </c>
-      <c r="U34" t="s">
-        <v>11</v>
-      </c>
-      <c r="V34" t="s">
-        <v>39</v>
-      </c>
-      <c r="W34" t="s">
-        <v>43</v>
-      </c>
       <c r="X34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
@@ -2882,73 +2892,73 @@
         <v>26</v>
       </c>
       <c r="B35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" t="s">
         <v>90</v>
       </c>
-      <c r="C35" t="s">
-        <v>91</v>
-      </c>
       <c r="D35" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K35" s="2">
         <v>0</v>
       </c>
       <c r="L35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="S35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="X35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
@@ -2956,73 +2966,73 @@
         <v>27</v>
       </c>
       <c r="B36" t="s">
+        <v>91</v>
+      </c>
+      <c r="C36" t="s">
         <v>92</v>
       </c>
-      <c r="C36" t="s">
-        <v>93</v>
-      </c>
       <c r="D36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K36" s="2">
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="S36" t="s">
+        <v>41</v>
+      </c>
+      <c r="T36" t="s">
+        <v>10</v>
+      </c>
+      <c r="U36" t="s">
+        <v>10</v>
+      </c>
+      <c r="V36" t="s">
+        <v>38</v>
+      </c>
+      <c r="W36" t="s">
         <v>42</v>
       </c>
-      <c r="T36" t="s">
-        <v>11</v>
-      </c>
-      <c r="U36" t="s">
-        <v>11</v>
-      </c>
-      <c r="V36" t="s">
-        <v>39</v>
-      </c>
-      <c r="W36" t="s">
-        <v>43</v>
-      </c>
       <c r="X36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
@@ -3030,73 +3040,73 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" t="s">
         <v>94</v>
       </c>
-      <c r="C37" t="s">
-        <v>95</v>
-      </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K37" s="2">
         <v>1</v>
       </c>
       <c r="L37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="S37" t="s">
+        <v>41</v>
+      </c>
+      <c r="T37" t="s">
+        <v>10</v>
+      </c>
+      <c r="U37" t="s">
+        <v>10</v>
+      </c>
+      <c r="V37" t="s">
+        <v>38</v>
+      </c>
+      <c r="W37" t="s">
         <v>42</v>
       </c>
-      <c r="T37" t="s">
-        <v>11</v>
-      </c>
-      <c r="U37" t="s">
-        <v>11</v>
-      </c>
-      <c r="V37" t="s">
-        <v>39</v>
-      </c>
-      <c r="W37" t="s">
-        <v>43</v>
-      </c>
       <c r="X37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
@@ -3104,73 +3114,73 @@
         <v>29</v>
       </c>
       <c r="B38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K38" s="2">
         <v>0</v>
       </c>
       <c r="L38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R38" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="S38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="X38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
@@ -3178,22 +3188,22 @@
         <v>30</v>
       </c>
       <c r="B39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" t="s">
         <v>97</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
+        <v>34</v>
+      </c>
+      <c r="E39" t="s">
         <v>98</v>
       </c>
-      <c r="D39" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" t="s">
-        <v>99</v>
-      </c>
       <c r="F39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H39" s="1">
         <v>46148.375</v>
@@ -3202,49 +3212,49 @@
         <v>46150.708333333299</v>
       </c>
       <c r="J39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K39" s="2">
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R39" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
@@ -3252,22 +3262,22 @@
         <v>31</v>
       </c>
       <c r="B40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" t="s">
         <v>100</v>
       </c>
-      <c r="C40" t="s">
-        <v>101</v>
-      </c>
       <c r="D40" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H40" s="1">
         <v>46148.375</v>
@@ -3276,49 +3286,49 @@
         <v>46150.708333333299</v>
       </c>
       <c r="J40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K40" s="2">
         <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R40" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="S40" t="s">
+        <v>41</v>
+      </c>
+      <c r="T40" t="s">
+        <v>10</v>
+      </c>
+      <c r="U40" t="s">
+        <v>10</v>
+      </c>
+      <c r="V40" t="s">
+        <v>38</v>
+      </c>
+      <c r="W40" t="s">
         <v>42</v>
       </c>
-      <c r="T40" t="s">
-        <v>11</v>
-      </c>
-      <c r="U40" t="s">
-        <v>11</v>
-      </c>
-      <c r="V40" t="s">
-        <v>39</v>
-      </c>
-      <c r="W40" t="s">
-        <v>43</v>
-      </c>
       <c r="X40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
@@ -3326,22 +3336,22 @@
         <v>32</v>
       </c>
       <c r="B41" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" t="s">
         <v>102</v>
       </c>
-      <c r="C41" t="s">
-        <v>103</v>
-      </c>
       <c r="D41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H41" s="1">
         <v>46148.375</v>
@@ -3350,49 +3360,49 @@
         <v>46150.708333333299</v>
       </c>
       <c r="J41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K41" s="2">
         <v>1</v>
       </c>
       <c r="L41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R41" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="S41" t="s">
+        <v>41</v>
+      </c>
+      <c r="T41" t="s">
+        <v>10</v>
+      </c>
+      <c r="U41" t="s">
+        <v>10</v>
+      </c>
+      <c r="V41" t="s">
+        <v>38</v>
+      </c>
+      <c r="W41" t="s">
         <v>42</v>
       </c>
-      <c r="T41" t="s">
-        <v>11</v>
-      </c>
-      <c r="U41" t="s">
-        <v>11</v>
-      </c>
-      <c r="V41" t="s">
-        <v>39</v>
-      </c>
-      <c r="W41" t="s">
-        <v>43</v>
-      </c>
       <c r="X41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
@@ -3400,22 +3410,22 @@
         <v>33</v>
       </c>
       <c r="B42" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" t="s">
         <v>104</v>
       </c>
-      <c r="C42" t="s">
-        <v>105</v>
-      </c>
       <c r="D42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H42" s="1">
         <v>46148.375</v>
@@ -3424,49 +3434,49 @@
         <v>46150.708333333299</v>
       </c>
       <c r="J42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K42" s="2">
         <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q42" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R42" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S42" t="s">
+        <v>41</v>
+      </c>
+      <c r="T42" t="s">
+        <v>10</v>
+      </c>
+      <c r="U42" t="s">
+        <v>10</v>
+      </c>
+      <c r="V42" t="s">
+        <v>38</v>
+      </c>
+      <c r="W42" t="s">
         <v>42</v>
       </c>
-      <c r="T42" t="s">
-        <v>11</v>
-      </c>
-      <c r="U42" t="s">
-        <v>11</v>
-      </c>
-      <c r="V42" t="s">
-        <v>39</v>
-      </c>
-      <c r="W42" t="s">
-        <v>43</v>
-      </c>
       <c r="X42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
@@ -3474,22 +3484,22 @@
         <v>34</v>
       </c>
       <c r="B43" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43" t="s">
         <v>106</v>
       </c>
-      <c r="C43" t="s">
-        <v>107</v>
-      </c>
       <c r="D43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H43" s="1">
         <v>46148.375</v>
@@ -3498,49 +3508,49 @@
         <v>46150.708333333299</v>
       </c>
       <c r="J43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K43" s="2">
         <v>1</v>
       </c>
       <c r="L43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R43" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="S43" t="s">
+        <v>41</v>
+      </c>
+      <c r="T43" t="s">
+        <v>10</v>
+      </c>
+      <c r="U43" t="s">
+        <v>10</v>
+      </c>
+      <c r="V43" t="s">
+        <v>38</v>
+      </c>
+      <c r="W43" t="s">
         <v>42</v>
       </c>
-      <c r="T43" t="s">
-        <v>11</v>
-      </c>
-      <c r="U43" t="s">
-        <v>11</v>
-      </c>
-      <c r="V43" t="s">
-        <v>39</v>
-      </c>
-      <c r="W43" t="s">
-        <v>43</v>
-      </c>
       <c r="X43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.25">
@@ -3548,22 +3558,22 @@
         <v>35</v>
       </c>
       <c r="B44" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" t="s">
         <v>108</v>
       </c>
-      <c r="C44" t="s">
-        <v>109</v>
-      </c>
       <c r="D44" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H44" s="1">
         <v>46148.375</v>
@@ -3572,49 +3582,49 @@
         <v>46150.708333333299</v>
       </c>
       <c r="J44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K44" s="2">
         <v>1</v>
       </c>
       <c r="L44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R44" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="S44" t="s">
+        <v>41</v>
+      </c>
+      <c r="T44" t="s">
+        <v>10</v>
+      </c>
+      <c r="U44" t="s">
+        <v>10</v>
+      </c>
+      <c r="V44" t="s">
+        <v>38</v>
+      </c>
+      <c r="W44" t="s">
         <v>42</v>
       </c>
-      <c r="T44" t="s">
-        <v>11</v>
-      </c>
-      <c r="U44" t="s">
-        <v>11</v>
-      </c>
-      <c r="V44" t="s">
-        <v>39</v>
-      </c>
-      <c r="W44" t="s">
-        <v>43</v>
-      </c>
       <c r="X44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
@@ -3622,22 +3632,22 @@
         <v>36</v>
       </c>
       <c r="B45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" t="s">
         <v>110</v>
       </c>
-      <c r="C45" t="s">
-        <v>111</v>
-      </c>
       <c r="D45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H45" s="1">
         <v>46148.375</v>
@@ -3646,49 +3656,49 @@
         <v>46150.708333333299</v>
       </c>
       <c r="J45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K45" s="2">
         <v>1</v>
       </c>
       <c r="L45" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R45" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="S45" t="s">
+        <v>41</v>
+      </c>
+      <c r="T45" t="s">
+        <v>10</v>
+      </c>
+      <c r="U45" t="s">
+        <v>10</v>
+      </c>
+      <c r="V45" t="s">
+        <v>38</v>
+      </c>
+      <c r="W45" t="s">
         <v>42</v>
       </c>
-      <c r="T45" t="s">
-        <v>11</v>
-      </c>
-      <c r="U45" t="s">
-        <v>11</v>
-      </c>
-      <c r="V45" t="s">
-        <v>39</v>
-      </c>
-      <c r="W45" t="s">
-        <v>43</v>
-      </c>
       <c r="X45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.25">
@@ -3696,22 +3706,22 @@
         <v>37</v>
       </c>
       <c r="B46" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46" t="s">
         <v>112</v>
       </c>
-      <c r="C46" t="s">
-        <v>113</v>
-      </c>
       <c r="D46" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H46" s="1">
         <v>46148.375</v>
@@ -3720,49 +3730,49 @@
         <v>46150.708333333299</v>
       </c>
       <c r="J46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K46" s="2">
         <v>0</v>
       </c>
       <c r="L46" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R46" t="s">
-        <v>11</v>
+        <v>163</v>
       </c>
       <c r="S46" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="T46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="X46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
@@ -3770,22 +3780,22 @@
         <v>38</v>
       </c>
       <c r="B47" t="s">
+        <v>113</v>
+      </c>
+      <c r="C47" t="s">
         <v>114</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
+        <v>34</v>
+      </c>
+      <c r="E47" t="s">
         <v>115</v>
       </c>
-      <c r="D47" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" t="s">
-        <v>116</v>
-      </c>
       <c r="F47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H47" s="1">
         <v>46148.375</v>
@@ -3794,49 +3804,49 @@
         <v>46148.708333333299</v>
       </c>
       <c r="J47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K47" s="2">
         <v>1</v>
       </c>
       <c r="L47" t="s">
-        <v>11</v>
+        <v>124</v>
       </c>
       <c r="M47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q47" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R47" t="s">
-        <v>11</v>
+        <v>164</v>
       </c>
       <c r="S47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.25">
@@ -3844,22 +3854,22 @@
         <v>39</v>
       </c>
       <c r="B48" t="s">
+        <v>116</v>
+      </c>
+      <c r="C48" t="s">
         <v>117</v>
       </c>
-      <c r="C48" t="s">
-        <v>118</v>
-      </c>
       <c r="D48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E48" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H48" s="1">
         <v>46148.375</v>
@@ -3868,49 +3878,49 @@
         <v>46148.708333333299</v>
       </c>
       <c r="J48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K48" s="2">
         <v>1</v>
       </c>
       <c r="L48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R48" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S48" t="s">
+        <v>41</v>
+      </c>
+      <c r="T48" t="s">
+        <v>10</v>
+      </c>
+      <c r="U48" t="s">
+        <v>10</v>
+      </c>
+      <c r="V48" t="s">
+        <v>38</v>
+      </c>
+      <c r="W48" t="s">
         <v>42</v>
       </c>
-      <c r="T48" t="s">
-        <v>11</v>
-      </c>
-      <c r="U48" t="s">
-        <v>11</v>
-      </c>
-      <c r="V48" t="s">
-        <v>39</v>
-      </c>
-      <c r="W48" t="s">
-        <v>43</v>
-      </c>
       <c r="X48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.25">
@@ -3918,73 +3928,73 @@
         <v>40</v>
       </c>
       <c r="B49" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" t="s">
         <v>119</v>
       </c>
-      <c r="C49" t="s">
-        <v>120</v>
-      </c>
       <c r="D49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K49" s="2">
         <v>1</v>
       </c>
       <c r="L49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R49" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="S49" t="s">
+        <v>41</v>
+      </c>
+      <c r="T49" t="s">
+        <v>10</v>
+      </c>
+      <c r="U49" t="s">
+        <v>10</v>
+      </c>
+      <c r="V49" t="s">
+        <v>38</v>
+      </c>
+      <c r="W49" t="s">
         <v>42</v>
       </c>
-      <c r="T49" t="s">
-        <v>11</v>
-      </c>
-      <c r="U49" t="s">
-        <v>11</v>
-      </c>
-      <c r="V49" t="s">
-        <v>39</v>
-      </c>
-      <c r="W49" t="s">
-        <v>43</v>
-      </c>
       <c r="X49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.25">
@@ -3992,73 +4002,73 @@
         <v>41</v>
       </c>
       <c r="B50" t="s">
+        <v>120</v>
+      </c>
+      <c r="C50" t="s">
         <v>121</v>
       </c>
-      <c r="C50" t="s">
-        <v>122</v>
-      </c>
       <c r="D50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K50" s="2">
         <v>1</v>
       </c>
       <c r="L50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R50" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="S50" t="s">
+        <v>41</v>
+      </c>
+      <c r="T50" t="s">
+        <v>10</v>
+      </c>
+      <c r="U50" t="s">
+        <v>10</v>
+      </c>
+      <c r="V50" t="s">
+        <v>38</v>
+      </c>
+      <c r="W50" t="s">
         <v>42</v>
       </c>
-      <c r="T50" t="s">
-        <v>11</v>
-      </c>
-      <c r="U50" t="s">
-        <v>11</v>
-      </c>
-      <c r="V50" t="s">
-        <v>39</v>
-      </c>
-      <c r="W50" t="s">
-        <v>43</v>
-      </c>
       <c r="X50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.25">
@@ -4066,79 +4076,79 @@
         <v>42</v>
       </c>
       <c r="B51" t="s">
+        <v>122</v>
+      </c>
+      <c r="C51" t="s">
         <v>123</v>
       </c>
-      <c r="C51" t="s">
-        <v>124</v>
-      </c>
       <c r="D51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K51" s="2">
         <v>1</v>
       </c>
       <c r="L51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R51" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S51" t="s">
+        <v>41</v>
+      </c>
+      <c r="T51" t="s">
+        <v>10</v>
+      </c>
+      <c r="U51" t="s">
+        <v>10</v>
+      </c>
+      <c r="V51" t="s">
+        <v>38</v>
+      </c>
+      <c r="W51" t="s">
         <v>42</v>
       </c>
-      <c r="T51" t="s">
-        <v>11</v>
-      </c>
-      <c r="U51" t="s">
-        <v>11</v>
-      </c>
-      <c r="V51" t="s">
-        <v>39</v>
-      </c>
-      <c r="W51" t="s">
-        <v>43</v>
-      </c>
       <c r="X51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:X5 A23:J23 A11:J11 M11:Q11 A12:J12 M12:Q12 A13:J13 M13:Q13 A14:J14 M14:Q14 A15:J15 M15:Q15 A16:J16 M16:Q16 A17:J17 M17:Q17 A18:J18 M18:Q18 A19:J19 M19:Q19 A20:J20 M20:Q20 A21:J21 M21:Q21 A22:J22 M22:Q22 A28:J28 A24:J24 M24:Q24 A25:J25 M25:Q25 A26:J26 M26:Q26 A27:J27 M27:Q27 A39:J39 A29:J29 M29:Q29 A30:J30 M30:Q30 A31:J31 M31:Q31 A32:J32 M32:Q32 A33:J33 M33:Q33 A34:J34 M34:Q34 A35:K35 M35:Q35 A36:J36 M36:Q36 A37:J37 M37:Q37 A38:K38 M38:X38 A47:J47 A40:J40 M40:Q40 A41:J41 M41:Q41 A42:J42 M42:Q42 A43:J43 M43:Q43 A44:J44 M44:Q44 A45:J45 M45:Q45 A46:K46 M46:X46 A51:J51 A48:J48 M48:Q48 A49:J49 M49:Q49 A50:J50 M50:Q50 M51:Q51 S11:X11 S12:X12 S13:X13 S14:X14 S15:X15 S16:X16 T17:X17 S18:X18 S19:X19 S20:X20 S21:X21 S22:X22 T23:X23 S24:X24 S25:X25 S26:X26 S27:X27 T28:X28 S29:X29 S30:X30 S31:X31 S32:X32 S33:X33 T34:X34 S35:X35 S36:X36 S37:X37 T39:X39 T40:X40 T41:X41 T42:X42 T43:X43 S45:X45 S48:X48 S49:X49 S50:X50 S51:X51 A7:X9 A6 C6:X6 M23:Q23 M28:Q28 M39:Q39 T44:X44 A10:J10 M10:R10 L47:X47 T10:X10" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:X5 A23:C23 A11:C11 M11:Q11 A12:C12 M12:Q12 A13:C13 M13:Q13 A14:C14 M14:Q14 A15:C15 M15:Q15 A16:C16 M16:Q16 A17:C17 M17:Q17 A18:C18 M18:Q18 A19:C19 M19:Q19 A20:C20 M20:Q20 A21:C21 M21:Q21 A22:C22 M22:Q22 A28:C28 A24:C24 M24:Q24 A25:C25 M25:Q25 A26:C26 M26:Q26 A27:C27 M27:Q27 A39:C39 A29:C29 M29:Q29 A30:C30 M30:Q30 A31:C31 M31:Q31 A32:C32 M32:Q32 A33:C33 M33:Q33 A34:C34 M34:Q34 A35:C35 M35:Q35 A36:C36 M36:Q36 A37:C37 M37:Q37 A38:C38 M38:Q38 A47:C47 A40:C40 M40:Q40 A41:C41 M41:Q41 A42:C42 M42:Q42 A43:C43 M43:Q43 A44:C44 M44:Q44 A45:C45 N45:Q45 A46:C46 N46:Q46 A51:C51 A48:C48 N48:Q48 A49:C49 N49:Q49 A50:C50 N50:Q50 N51:Q51 S11:X11 S12:X12 S13:X13 S14:X14 S15:X15 S16:X16 T17:X17 S18:X18 S19:X19 S20:X20 S21:X21 S22:X22 T23:X23 S24:X24 S25:X25 S26:X26 S27:X27 T28:X28 S29:X29 S30:X30 S31:X31 S32:X32 S33:X33 T34:X34 S35:X35 S36:X36 S37:X37 T39:X39 T40:X40 T41:X41 T42:X42 T43:X43 S45:X45 S48:X48 S49:X49 S50:X50 S51:X51 A8:X9 A6 C6:X6 M23:Q23 M28:Q28 M39:Q39 T44:X44 A10:J10 M10:R10 N47:Q47 T10:X10 E23:J23 E11:J11 E12:G12 E13:J13 E14:J14 E15:J15 E16:J16 E17:J17 E18:J18 E19:J19 E20:J20 E21:J21 E22:J22 E28:J28 E24:J24 E25:J25 E26:J26 E27:J27 E39:J39 E29:J29 E30:J30 E31:J31 E32:J32 E33:J33 E34:J34 E35:K35 E36:J36 E37:J37 E38:K38 E47:J47 E40:J40 E41:J41 E42:J42 E43:J43 E44:J44 E45:J45 E46:K46 E51:J51 E48:J48 E49:J49 E50:J50 J12 S38:X38 T46:X46 S47:X47 A7 D7:X7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Robot Monitoring.xlsx
+++ b/Robot Monitoring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\robot_dashboard\robot-navigasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8D08BC-E6DA-4EBC-A423-463731C2CA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A9CB19-CFE8-4299-ABEC-FEE2D48409F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -328,9 +328,6 @@
     <t>4.2</t>
   </si>
   <si>
-    <t>Notifikasi otomatis (Email, SMS, WhatsApp, App)</t>
-  </si>
-  <si>
     <t>4.3</t>
   </si>
   <si>
@@ -518,6 +515,9 @@
   </si>
   <si>
     <t>Thu May 07 2026 15:04:15 GMT+0700 (Indonesia Time)</t>
+  </si>
+  <si>
+    <t>Notifikasi otomatis (Email,App)</t>
   </si>
 </sst>
 </file>
@@ -536,12 +536,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -556,13 +574,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -901,7 +922,7 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5" customWidth="1"/>
+    <col min="3" max="3" width="59.75" customWidth="1"/>
     <col min="8" max="9" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -958,7 +979,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -1047,7 +1068,7 @@
       <c r="B10" t="s">
         <v>32</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D10" t="s">
@@ -1075,7 +1096,7 @@
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M10" t="s">
         <v>10</v>
@@ -1121,7 +1142,7 @@
       <c r="B11" t="s">
         <v>39</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D11" t="s">
@@ -1149,7 +1170,7 @@
         <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -1167,7 +1188,7 @@
         <v>36</v>
       </c>
       <c r="R11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="S11" t="s">
         <v>41</v>
@@ -1195,7 +1216,7 @@
       <c r="B12" t="s">
         <v>43</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D12" t="s">
@@ -1220,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -1238,7 +1259,7 @@
         <v>36</v>
       </c>
       <c r="R12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S12" t="s">
         <v>41</v>
@@ -1266,7 +1287,7 @@
       <c r="B13" t="s">
         <v>45</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="4" t="s">
         <v>46</v>
       </c>
       <c r="D13" t="s">
@@ -1294,7 +1315,7 @@
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -1312,7 +1333,7 @@
         <v>36</v>
       </c>
       <c r="R13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s">
         <v>41</v>
@@ -1340,7 +1361,7 @@
       <c r="B14" t="s">
         <v>47</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="4" t="s">
         <v>48</v>
       </c>
       <c r="D14" t="s">
@@ -1368,7 +1389,7 @@
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -1386,7 +1407,7 @@
         <v>36</v>
       </c>
       <c r="R14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S14" t="s">
         <v>41</v>
@@ -1414,7 +1435,7 @@
       <c r="B15" t="s">
         <v>49</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="4" t="s">
         <v>50</v>
       </c>
       <c r="D15" t="s">
@@ -1442,7 +1463,7 @@
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -1460,7 +1481,7 @@
         <v>36</v>
       </c>
       <c r="R15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S15" t="s">
         <v>41</v>
@@ -1488,7 +1509,7 @@
       <c r="B16" t="s">
         <v>51</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D16" t="s">
@@ -1516,7 +1537,7 @@
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -1534,7 +1555,7 @@
         <v>36</v>
       </c>
       <c r="R16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S16" t="s">
         <v>41</v>
@@ -1562,7 +1583,7 @@
       <c r="B17" t="s">
         <v>53</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="4" t="s">
         <v>54</v>
       </c>
       <c r="D17" t="s">
@@ -1590,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -1608,7 +1629,7 @@
         <v>36</v>
       </c>
       <c r="R17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="S17" t="s">
         <v>41</v>
@@ -1636,7 +1657,7 @@
       <c r="B18" t="s">
         <v>55</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="4" t="s">
         <v>56</v>
       </c>
       <c r="D18" t="s">
@@ -1664,7 +1685,7 @@
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -1682,7 +1703,7 @@
         <v>36</v>
       </c>
       <c r="R18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S18" t="s">
         <v>41</v>
@@ -1710,7 +1731,7 @@
       <c r="B19" t="s">
         <v>57</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D19" t="s">
@@ -1738,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -1756,7 +1777,7 @@
         <v>36</v>
       </c>
       <c r="R19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="S19" t="s">
         <v>41</v>
@@ -1784,7 +1805,7 @@
       <c r="B20" t="s">
         <v>59</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="4" t="s">
         <v>60</v>
       </c>
       <c r="D20" t="s">
@@ -1812,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="L20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -1830,7 +1851,7 @@
         <v>36</v>
       </c>
       <c r="R20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S20" t="s">
         <v>41</v>
@@ -1858,7 +1879,7 @@
       <c r="B21" t="s">
         <v>61</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="4" t="s">
         <v>62</v>
       </c>
       <c r="D21" t="s">
@@ -1886,7 +1907,7 @@
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -1904,7 +1925,7 @@
         <v>36</v>
       </c>
       <c r="R21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S21" t="s">
         <v>41</v>
@@ -1932,7 +1953,7 @@
       <c r="B22" t="s">
         <v>63</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D22" t="s">
@@ -1960,7 +1981,7 @@
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -1978,7 +1999,7 @@
         <v>36</v>
       </c>
       <c r="R22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S22" t="s">
         <v>41</v>
@@ -2006,7 +2027,7 @@
       <c r="B23" t="s">
         <v>65</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D23" t="s">
@@ -2034,7 +2055,7 @@
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -2052,7 +2073,7 @@
         <v>41</v>
       </c>
       <c r="R23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S23" t="s">
         <v>41</v>
@@ -2080,7 +2101,7 @@
       <c r="B24" t="s">
         <v>67</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="4" t="s">
         <v>68</v>
       </c>
       <c r="D24" t="s">
@@ -2108,7 +2129,7 @@
         <v>1</v>
       </c>
       <c r="L24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -2126,7 +2147,7 @@
         <v>36</v>
       </c>
       <c r="R24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S24" t="s">
         <v>41</v>
@@ -2154,7 +2175,7 @@
       <c r="B25" t="s">
         <v>69</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="4" t="s">
         <v>70</v>
       </c>
       <c r="D25" t="s">
@@ -2182,7 +2203,7 @@
         <v>1</v>
       </c>
       <c r="L25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -2200,7 +2221,7 @@
         <v>36</v>
       </c>
       <c r="R25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S25" t="s">
         <v>41</v>
@@ -2228,7 +2249,7 @@
       <c r="B26" t="s">
         <v>71</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="4" t="s">
         <v>72</v>
       </c>
       <c r="D26" t="s">
@@ -2256,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="L26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -2274,7 +2295,7 @@
         <v>36</v>
       </c>
       <c r="R26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S26" t="s">
         <v>41</v>
@@ -2302,7 +2323,7 @@
       <c r="B27" t="s">
         <v>73</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="4" t="s">
         <v>74</v>
       </c>
       <c r="D27" t="s">
@@ -2330,7 +2351,7 @@
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -2348,7 +2369,7 @@
         <v>36</v>
       </c>
       <c r="R27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S27" t="s">
         <v>41</v>
@@ -2376,7 +2397,7 @@
       <c r="B28" t="s">
         <v>75</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="4" t="s">
         <v>76</v>
       </c>
       <c r="D28" t="s">
@@ -2404,7 +2425,7 @@
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M28" t="s">
         <v>10</v>
@@ -2422,7 +2443,7 @@
         <v>41</v>
       </c>
       <c r="R28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="S28" t="s">
         <v>41</v>
@@ -2450,7 +2471,7 @@
       <c r="B29" t="s">
         <v>77</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="4" t="s">
         <v>78</v>
       </c>
       <c r="D29" t="s">
@@ -2478,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="L29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M29" t="s">
         <v>10</v>
@@ -2496,7 +2517,7 @@
         <v>36</v>
       </c>
       <c r="R29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="S29" t="s">
         <v>41</v>
@@ -2524,7 +2545,7 @@
       <c r="B30" t="s">
         <v>79</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="4" t="s">
         <v>80</v>
       </c>
       <c r="D30" t="s">
@@ -2552,7 +2573,7 @@
         <v>1</v>
       </c>
       <c r="L30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M30" t="s">
         <v>10</v>
@@ -2570,7 +2591,7 @@
         <v>36</v>
       </c>
       <c r="R30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="S30" t="s">
         <v>41</v>
@@ -2598,7 +2619,7 @@
       <c r="B31" t="s">
         <v>81</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="4" t="s">
         <v>82</v>
       </c>
       <c r="D31" t="s">
@@ -2626,7 +2647,7 @@
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M31" t="s">
         <v>10</v>
@@ -2644,7 +2665,7 @@
         <v>36</v>
       </c>
       <c r="R31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S31" t="s">
         <v>41</v>
@@ -2672,7 +2693,7 @@
       <c r="B32" t="s">
         <v>83</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="4" t="s">
         <v>84</v>
       </c>
       <c r="D32" t="s">
@@ -2700,7 +2721,7 @@
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M32" t="s">
         <v>10</v>
@@ -2718,7 +2739,7 @@
         <v>36</v>
       </c>
       <c r="R32" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="S32" t="s">
         <v>41</v>
@@ -2746,7 +2767,7 @@
       <c r="B33" t="s">
         <v>85</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="4" t="s">
         <v>86</v>
       </c>
       <c r="D33" t="s">
@@ -2774,7 +2795,7 @@
         <v>1</v>
       </c>
       <c r="L33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M33" t="s">
         <v>10</v>
@@ -2792,7 +2813,7 @@
         <v>36</v>
       </c>
       <c r="R33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S33" t="s">
         <v>41</v>
@@ -2820,7 +2841,7 @@
       <c r="B34" t="s">
         <v>87</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="4" t="s">
         <v>88</v>
       </c>
       <c r="D34" t="s">
@@ -2848,7 +2869,7 @@
         <v>1</v>
       </c>
       <c r="L34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M34" t="s">
         <v>10</v>
@@ -2866,7 +2887,7 @@
         <v>36</v>
       </c>
       <c r="R34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="S34" t="s">
         <v>41</v>
@@ -2894,7 +2915,7 @@
       <c r="B35" t="s">
         <v>89</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="5" t="s">
         <v>90</v>
       </c>
       <c r="D35" t="s">
@@ -2922,7 +2943,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M35" t="s">
         <v>10</v>
@@ -2940,7 +2961,7 @@
         <v>36</v>
       </c>
       <c r="R35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="S35" t="s">
         <v>10</v>
@@ -2968,7 +2989,7 @@
       <c r="B36" t="s">
         <v>91</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="4" t="s">
         <v>92</v>
       </c>
       <c r="D36" t="s">
@@ -2996,7 +3017,7 @@
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M36" t="s">
         <v>10</v>
@@ -3014,7 +3035,7 @@
         <v>36</v>
       </c>
       <c r="R36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="S36" t="s">
         <v>41</v>
@@ -3042,7 +3063,7 @@
       <c r="B37" t="s">
         <v>93</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="4" t="s">
         <v>94</v>
       </c>
       <c r="D37" t="s">
@@ -3070,7 +3091,7 @@
         <v>1</v>
       </c>
       <c r="L37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M37" t="s">
         <v>10</v>
@@ -3088,7 +3109,7 @@
         <v>36</v>
       </c>
       <c r="R37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="S37" t="s">
         <v>41</v>
@@ -3116,7 +3137,7 @@
       <c r="B38" t="s">
         <v>95</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="5" t="s">
         <v>90</v>
       </c>
       <c r="D38" t="s">
@@ -3144,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="L38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M38" t="s">
         <v>10</v>
@@ -3162,7 +3183,7 @@
         <v>36</v>
       </c>
       <c r="R38" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="S38" t="s">
         <v>10</v>
@@ -3190,7 +3211,7 @@
       <c r="B39" t="s">
         <v>96</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="4" t="s">
         <v>97</v>
       </c>
       <c r="D39" t="s">
@@ -3218,7 +3239,7 @@
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M39" t="s">
         <v>10</v>
@@ -3236,7 +3257,7 @@
         <v>36</v>
       </c>
       <c r="R39" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="S39" t="s">
         <v>41</v>
@@ -3264,7 +3285,7 @@
       <c r="B40" t="s">
         <v>99</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="6" t="s">
         <v>100</v>
       </c>
       <c r="D40" t="s">
@@ -3292,7 +3313,7 @@
         <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M40" t="s">
         <v>10</v>
@@ -3310,7 +3331,7 @@
         <v>36</v>
       </c>
       <c r="R40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="S40" t="s">
         <v>41</v>
@@ -3338,8 +3359,8 @@
       <c r="B41" t="s">
         <v>101</v>
       </c>
-      <c r="C41" t="s">
-        <v>102</v>
+      <c r="C41" s="6" t="s">
+        <v>165</v>
       </c>
       <c r="D41" t="s">
         <v>34</v>
@@ -3366,7 +3387,7 @@
         <v>1</v>
       </c>
       <c r="L41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M41" t="s">
         <v>10</v>
@@ -3384,7 +3405,7 @@
         <v>36</v>
       </c>
       <c r="R41" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S41" t="s">
         <v>41</v>
@@ -3410,10 +3431,10 @@
         <v>33</v>
       </c>
       <c r="B42" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="C42" t="s">
-        <v>104</v>
       </c>
       <c r="D42" t="s">
         <v>34</v>
@@ -3440,7 +3461,7 @@
         <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M42" t="s">
         <v>10</v>
@@ -3458,7 +3479,7 @@
         <v>36</v>
       </c>
       <c r="R42" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="S42" t="s">
         <v>41</v>
@@ -3484,10 +3505,10 @@
         <v>34</v>
       </c>
       <c r="B43" t="s">
+        <v>104</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="C43" t="s">
-        <v>106</v>
       </c>
       <c r="D43" t="s">
         <v>34</v>
@@ -3514,7 +3535,7 @@
         <v>1</v>
       </c>
       <c r="L43" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M43" t="s">
         <v>10</v>
@@ -3532,7 +3553,7 @@
         <v>36</v>
       </c>
       <c r="R43" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="S43" t="s">
         <v>41</v>
@@ -3558,10 +3579,10 @@
         <v>35</v>
       </c>
       <c r="B44" t="s">
+        <v>106</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="C44" t="s">
-        <v>108</v>
       </c>
       <c r="D44" t="s">
         <v>34</v>
@@ -3588,7 +3609,7 @@
         <v>1</v>
       </c>
       <c r="L44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M44" t="s">
         <v>10</v>
@@ -3606,7 +3627,7 @@
         <v>36</v>
       </c>
       <c r="R44" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="S44" t="s">
         <v>41</v>
@@ -3632,10 +3653,10 @@
         <v>36</v>
       </c>
       <c r="B45" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="C45" t="s">
-        <v>110</v>
       </c>
       <c r="D45" t="s">
         <v>34</v>
@@ -3662,7 +3683,7 @@
         <v>1</v>
       </c>
       <c r="L45" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M45" t="s">
         <v>10</v>
@@ -3680,7 +3701,7 @@
         <v>36</v>
       </c>
       <c r="R45" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="S45" t="s">
         <v>41</v>
@@ -3706,10 +3727,10 @@
         <v>37</v>
       </c>
       <c r="B46" t="s">
+        <v>110</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="C46" t="s">
-        <v>112</v>
       </c>
       <c r="D46" t="s">
         <v>34</v>
@@ -3736,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M46" t="s">
         <v>10</v>
@@ -3754,7 +3775,7 @@
         <v>36</v>
       </c>
       <c r="R46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="S46" t="s">
         <v>41</v>
@@ -3780,16 +3801,16 @@
         <v>38</v>
       </c>
       <c r="B47" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
+        <v>34</v>
+      </c>
+      <c r="E47" t="s">
         <v>114</v>
-      </c>
-      <c r="D47" t="s">
-        <v>34</v>
-      </c>
-      <c r="E47" t="s">
-        <v>115</v>
       </c>
       <c r="F47" t="s">
         <v>10</v>
@@ -3810,7 +3831,7 @@
         <v>1</v>
       </c>
       <c r="L47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M47" t="s">
         <v>10</v>
@@ -3828,7 +3849,7 @@
         <v>36</v>
       </c>
       <c r="R47" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S47" t="s">
         <v>10</v>
@@ -3854,16 +3875,16 @@
         <v>39</v>
       </c>
       <c r="B48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C48" t="s">
-        <v>117</v>
-      </c>
       <c r="D48" t="s">
         <v>34</v>
       </c>
       <c r="E48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F48" t="s">
         <v>10</v>
@@ -3884,7 +3905,7 @@
         <v>1</v>
       </c>
       <c r="L48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M48" t="s">
         <v>10</v>
@@ -3902,7 +3923,7 @@
         <v>36</v>
       </c>
       <c r="R48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="S48" t="s">
         <v>41</v>
@@ -3928,10 +3949,10 @@
         <v>40</v>
       </c>
       <c r="B49" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="C49" t="s">
-        <v>119</v>
       </c>
       <c r="D49" t="s">
         <v>34</v>
@@ -3958,7 +3979,7 @@
         <v>1</v>
       </c>
       <c r="L49" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M49" t="s">
         <v>10</v>
@@ -3976,7 +3997,7 @@
         <v>36</v>
       </c>
       <c r="R49" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S49" t="s">
         <v>41</v>
@@ -4002,10 +4023,10 @@
         <v>41</v>
       </c>
       <c r="B50" t="s">
+        <v>119</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="C50" t="s">
-        <v>121</v>
       </c>
       <c r="D50" t="s">
         <v>34</v>
@@ -4032,7 +4053,7 @@
         <v>1</v>
       </c>
       <c r="L50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M50" t="s">
         <v>10</v>
@@ -4050,7 +4071,7 @@
         <v>36</v>
       </c>
       <c r="R50" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="S50" t="s">
         <v>41</v>
@@ -4076,10 +4097,10 @@
         <v>42</v>
       </c>
       <c r="B51" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="C51" t="s">
-        <v>123</v>
       </c>
       <c r="D51" t="s">
         <v>34</v>
@@ -4106,7 +4127,7 @@
         <v>1</v>
       </c>
       <c r="L51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M51" t="s">
         <v>10</v>
@@ -4124,7 +4145,7 @@
         <v>36</v>
       </c>
       <c r="R51" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="S51" t="s">
         <v>41</v>
@@ -4148,7 +4169,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:X5 A23:C23 A11:C11 M11:Q11 A12:C12 M12:Q12 A13:C13 M13:Q13 A14:C14 M14:Q14 A15:C15 M15:Q15 A16:C16 M16:Q16 A17:C17 M17:Q17 A18:C18 M18:Q18 A19:C19 M19:Q19 A20:C20 M20:Q20 A21:C21 M21:Q21 A22:C22 M22:Q22 A28:C28 A24:C24 M24:Q24 A25:C25 M25:Q25 A26:C26 M26:Q26 A27:C27 M27:Q27 A39:C39 A29:C29 M29:Q29 A30:C30 M30:Q30 A31:C31 M31:Q31 A32:C32 M32:Q32 A33:C33 M33:Q33 A34:C34 M34:Q34 A35:C35 M35:Q35 A36:C36 M36:Q36 A37:C37 M37:Q37 A38:C38 M38:Q38 A47:C47 A40:C40 M40:Q40 A41:C41 M41:Q41 A42:C42 M42:Q42 A43:C43 M43:Q43 A44:C44 M44:Q44 A45:C45 N45:Q45 A46:C46 N46:Q46 A51:C51 A48:C48 N48:Q48 A49:C49 N49:Q49 A50:C50 N50:Q50 N51:Q51 S11:X11 S12:X12 S13:X13 S14:X14 S15:X15 S16:X16 T17:X17 S18:X18 S19:X19 S20:X20 S21:X21 S22:X22 T23:X23 S24:X24 S25:X25 S26:X26 S27:X27 T28:X28 S29:X29 S30:X30 S31:X31 S32:X32 S33:X33 T34:X34 S35:X35 S36:X36 S37:X37 T39:X39 T40:X40 T41:X41 T42:X42 T43:X43 S45:X45 S48:X48 S49:X49 S50:X50 S51:X51 A8:X9 A6 C6:X6 M23:Q23 M28:Q28 M39:Q39 T44:X44 A10:J10 M10:R10 N47:Q47 T10:X10 E23:J23 E11:J11 E12:G12 E13:J13 E14:J14 E15:J15 E16:J16 E17:J17 E18:J18 E19:J19 E20:J20 E21:J21 E22:J22 E28:J28 E24:J24 E25:J25 E26:J26 E27:J27 E39:J39 E29:J29 E30:J30 E31:J31 E32:J32 E33:J33 E34:J34 E35:K35 E36:J36 E37:J37 E38:K38 E47:J47 E40:J40 E41:J41 E42:J42 E43:J43 E44:J44 E45:J45 E46:K46 E51:J51 E48:J48 E49:J49 E50:J50 J12 S38:X38 T46:X46 S47:X47 A7 D7:X7" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:X5 A23:C23 A11:C11 M11:Q11 A12:C12 M12:Q12 A13:C13 M13:Q13 A14:C14 M14:Q14 A15:C15 M15:Q15 A16:C16 M16:Q16 A17:C17 M17:Q17 A18:C18 M18:Q18 A19:C19 M19:Q19 A20:C20 M20:Q20 A21:C21 M21:Q21 A22:C22 M22:Q22 A28:C28 A24:C24 M24:Q24 A25:C25 M25:Q25 A26:C26 M26:Q26 A27:C27 M27:Q27 A39:C39 A29:C29 M29:Q29 A30:C30 M30:Q30 A31:C31 M31:Q31 A32:C32 M32:Q32 A33:C33 M33:Q33 A34:C34 M34:Q34 A35:C35 M35:Q35 A36:C36 M36:Q36 A37:C37 M37:Q37 A38:C38 M38:Q38 A47:C47 A40:C40 M40:Q40 A41:B41 M41:Q41 A42:C42 M42:Q42 A43:C43 M43:Q43 A44:C44 M44:Q44 A45:C45 N45:Q45 A46:C46 N46:Q46 A51:C51 A48:C48 N48:Q48 A49:C49 N49:Q49 A50:C50 N50:Q50 N51:Q51 S11:X11 S12:X12 S13:X13 S14:X14 S15:X15 S16:X16 T17:X17 S18:X18 S19:X19 S20:X20 S21:X21 S22:X22 T23:X23 S24:X24 S25:X25 S26:X26 S27:X27 T28:X28 S29:X29 S30:X30 S31:X31 S32:X32 S33:X33 T34:X34 S35:X35 S36:X36 S37:X37 T39:X39 T40:X40 T41:X41 T42:X42 T43:X43 S45:X45 S48:X48 S49:X49 S50:X50 S51:X51 A8:X9 A6 C6:X6 M23:Q23 M28:Q28 M39:Q39 T44:X44 A10:J10 M10:R10 N47:Q47 T10:X10 E23:J23 E11:J11 E12:G12 E13:J13 E14:J14 E15:J15 E16:J16 E17:J17 E18:J18 E19:J19 E20:J20 E21:J21 E22:J22 E28:J28 E24:J24 E25:J25 E26:J26 E27:J27 E39:J39 E29:J29 E30:J30 E31:J31 E32:J32 E33:J33 E34:J34 E35:K35 E36:J36 E37:J37 E38:K38 E47:J47 E40:J40 E41:J41 E42:J42 E43:J43 E44:J44 E45:J45 E46:K46 E51:J51 E48:J48 E49:J49 E50:J50 J12 S38:X38 T46:X46 S47:X47 A7 D7:X7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>